--- a/ZonasEscolares/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
+++ b/ZonasEscolares/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
+++ b/ZonasEscolares/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>001 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-6.23176</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.87242999999999</v>
-      </c>
-      <c r="I2" t="n">
-        <v>202</v>
-      </c>
-      <c r="J2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-6.23176</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.87243</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>002 RAQUEL ROBLES DE ROMAN</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-6.23159</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.87002</v>
-      </c>
-      <c r="I3" t="n">
-        <v>222</v>
-      </c>
-      <c r="J3" t="n">
-        <v>11</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-6.23159</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.87002</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>18002 MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-6.23219</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.87233000000001</v>
-      </c>
-      <c r="I4" t="n">
-        <v>811</v>
-      </c>
-      <c r="J4" t="n">
-        <v>41</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-6.23219</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.87233</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>811</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>18288 ISABEL LINCH DE RUBIO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-6.228869</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.87167100000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>678</v>
-      </c>
-      <c r="J5" t="n">
-        <v>33</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-6.228869</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.871671</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>SEMINARIO JESUS MARIA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-6.22841</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.87426000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>869</v>
-      </c>
-      <c r="J6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-6.22841</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.87426</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>SAN JUAN DE LA LIBERTAD</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-6.229318</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.865568</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1992</v>
-      </c>
-      <c r="J7" t="n">
-        <v>92</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-6.229318</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.865568</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>VIRGEN ASUNTA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-6.23028</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.86994</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1221</v>
-      </c>
-      <c r="J8" t="n">
-        <v>64</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-6.23028</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.86994</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-6.229541</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.864243</v>
-      </c>
-      <c r="I9" t="n">
-        <v>490</v>
-      </c>
-      <c r="J9" t="n">
-        <v>39</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-6.229541</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.864243</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>18001 MIGUEL RUBIO</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-6.23203</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.86993</v>
-      </c>
-      <c r="I10" t="n">
-        <v>550</v>
-      </c>
-      <c r="J10" t="n">
-        <v>34</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-6.23203</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.86993</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>18041 PURIFICACION CULQUI PUIQUIN</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-6.4843</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.81610000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>214</v>
-      </c>
-      <c r="J11" t="n">
-        <v>16</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-6.4843</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.8161</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>18006 / LOS ANGELES DE PEDRO CASTRO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-6.2169</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.866</v>
-      </c>
-      <c r="I12" t="n">
-        <v>420</v>
-      </c>
-      <c r="J12" t="n">
-        <v>29</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-6.2169</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.866</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>DIVINO SALVADOR</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-6.22884</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.8742</v>
-      </c>
-      <c r="I13" t="n">
-        <v>458</v>
-      </c>
-      <c r="J13" t="n">
-        <v>55</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-6.22884</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.8742</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>379 MUNDO MAGICO</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-6.21491</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.86072</v>
-      </c>
-      <c r="I14" t="n">
-        <v>219</v>
-      </c>
-      <c r="J14" t="n">
-        <v>12</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-6.21491</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.86072</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>ALFRED NOBEL</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-6.23021</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.87184000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>157</v>
-      </c>
-      <c r="J15" t="n">
-        <v>19</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-6.23021</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.87184</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>ALFRED NOBEL</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-6.23061</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.86856</v>
-      </c>
-      <c r="I16" t="n">
-        <v>357</v>
-      </c>
-      <c r="J16" t="n">
-        <v>28</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-6.23061</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.86856</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
+++ b/ZonasEscolares/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>774530</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18002 MARIA AUXILIADORA</t>
+          <t>379 MUNDO MAGICO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-6.23219</t>
+          <t>-6.21491</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.87233</t>
+          <t>-77.86072</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>219</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18288 ISABEL LINCH DE RUBIO</t>
+          <t>18041 PURIFICACION CULQUI PUIQUIN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.228869</t>
+          <t>-6.4843</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.871671</t>
+          <t>-77.8161</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>829820</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SEMINARIO JESUS MARIA</t>
+          <t>ALFRED NOBEL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.22841</t>
+          <t>-6.23021</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.87426</t>
+          <t>-77.87184</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>157</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>903947</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SAN JUAN DE LA LIBERTAD</t>
+          <t>ALFRED NOBEL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.229318</t>
+          <t>-6.23061</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.865568</t>
+          <t>-77.86856</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>357</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>178932</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>VIRGEN ASUNTA</t>
+          <t>18006 / LOS ANGELES DE PEDRO CASTRO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.23028</t>
+          <t>-6.2169</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.86994</t>
+          <t>-77.866</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>420</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>18288 ISABEL LINCH DE RUBIO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.229541</t>
+          <t>-6.228869</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.864243</t>
+          <t>-77.871671</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>678</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>279</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>18041 PURIFICACION CULQUI PUIQUIN</t>
+          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.4843</t>
+          <t>-6.229541</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.8161</t>
+          <t>-77.864243</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>490</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>178932</t>
+          <t>142</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18006 / LOS ANGELES DE PEDRO CASTRO</t>
+          <t>18002 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.2169</t>
+          <t>-6.23219</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.866</t>
+          <t>-77.87233</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>811</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>654556</t>
+          <t>241</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DIVINO SALVADOR</t>
+          <t>SEMINARIO JESUS MARIA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.22884</t>
+          <t>-6.22841</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.8742</t>
+          <t>-77.87426</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>869</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>774530</t>
+          <t>654556</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>379 MUNDO MAGICO</t>
+          <t>DIVINO SALVADOR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.21491</t>
+          <t>-6.22884</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.86072</t>
+          <t>-77.8742</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>458</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>829820</t>
+          <t>260</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ALFRED NOBEL</t>
+          <t>VIRGEN ASUNTA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.23021</t>
+          <t>-6.23028</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.87184</t>
+          <t>-77.86994</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>903947</t>
+          <t>255</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ALFRED NOBEL</t>
+          <t>SAN JUAN DE LA LIBERTAD</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.23061</t>
+          <t>-6.229318</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.86856</t>
+          <t>-77.865568</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">

--- a/ZonasEscolares/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
+++ b/ZonasEscolares/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>903947</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>001 NIÑO JESUS DE PRAGA</t>
+          <t>ALFRED NOBEL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-6.23176</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.87243</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>-6.23061</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.86856</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>829820</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>002 RAQUEL ROBLES DE ROMAN</t>
+          <t>ALFRED NOBEL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-6.23159</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.87002</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>-6.23021</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.87184</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -635,22 +635,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>-6.21491</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>-77.86072</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>654556</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>18041 PURIFICACION CULQUI PUIQUIN</t>
+          <t>DIVINO SALVADOR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.4843</t>
+          <t>458</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.8161</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-6.22884</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.8742</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>829820</t>
+          <t>178932</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ALFRED NOBEL</t>
+          <t>18006 / LOS ANGELES DE PEDRO CASTRO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-6.23021</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.87184</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>-6.2169</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.866</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>903947</t>
+          <t>000868</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ALFRED NOBEL</t>
+          <t>18041 PURIFICACION CULQUI PUIQUIN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.23061</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.86856</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>-6.4843</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.8161</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>178932</t>
+          <t>000316</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18006 / LOS ANGELES DE PEDRO CASTRO</t>
+          <t>18001 MIGUEL RUBIO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.2169</t>
+          <t>550</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.866</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>-6.23203</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-77.86993</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>000279</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>18288 ISABEL LINCH DE RUBIO</t>
+          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-6.228869</t>
+          <t>490</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.871671</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>-6.229541</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-77.864243</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>000260</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18001 MIGUEL RUBIO</t>
+          <t>VIRGEN ASUNTA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-6.23203</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.86993</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>-6.23028</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-77.86994</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>000255</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>SAN JUAN DE LA LIBERTAD</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.229541</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.864243</t>
+          <t>92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>-6.229318</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.865568</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>000241</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>18002 MARIA AUXILIADORA</t>
+          <t>SEMINARIO JESUS MARIA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-6.23219</t>
+          <t>869</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.87233</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>-6.22841</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-77.87426</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>000203</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SEMINARIO JESUS MARIA</t>
+          <t>18288 ISABEL LINCH DE RUBIO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-6.22841</t>
+          <t>678</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.87426</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>-6.228869</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-77.871671</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>654556</t>
+          <t>000142</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DIVINO SALVADOR</t>
+          <t>18002 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-6.22884</t>
+          <t>811</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.8742</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>-6.23219</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>-77.87233</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>000024</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>VIRGEN ASUNTA</t>
+          <t>002 RAQUEL ROBLES DE ROMAN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.23028</t>
+          <t>222</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.86994</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>-6.23159</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-77.87002</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>000019</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SAN JUAN DE LA LIBERTAD</t>
+          <t>001 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.229318</t>
+          <t>202</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.865568</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>-6.23176</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>-77.87243</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">

--- a/ZonasEscolares/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
+++ b/ZonasEscolares/excels/AMAZONAS-CHACHAPOYAS-CHACHAPOYAS.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
